--- a/artfynd/A 24176-2025 artfynd.xlsx
+++ b/artfynd/A 24176-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95865356</v>
+        <v>135221075</v>
       </c>
       <c r="B2" t="n">
-        <v>91872</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552745</v>
+        <v>552740</v>
       </c>
       <c r="R2" t="n">
-        <v>6946269</v>
+        <v>6946329</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,26 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95865355</v>
+        <v>135221082</v>
       </c>
       <c r="B3" t="n">
-        <v>83307</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552656</v>
+        <v>552676</v>
       </c>
       <c r="R3" t="n">
-        <v>6946299</v>
+        <v>6946256</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,19 +877,1634 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135221084</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83350</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>308</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552610</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6946410</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135221078</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552715</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6946331</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135221072</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552711</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6946235</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>95865356</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552745</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6946269</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135221073</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552723</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6946274</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135221077</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552718</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6946331</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135221079</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552709</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6946318</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135221083</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83341</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552609</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6946411</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95865355</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552656</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6946299</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135221080</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552694</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6946288</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135221071</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>552717</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6946225</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135221074</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>552743</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6946299</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135221081</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>552689</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6946286</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135221085</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>552577</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6946345</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135221076</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>552721</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6946333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24176-2025 artfynd.xlsx
+++ b/artfynd/A 24176-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221075</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221082</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221084</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221078</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221072</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95865356</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221073</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221077</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221079</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221083</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95865355</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221080</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2064,6 +2129,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221071</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221074</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221081</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2398,6 +2478,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221085</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2505,8 +2590,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221076</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24176-2025 artfynd.xlsx
+++ b/artfynd/A 24176-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135221075</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135221082</v>
       </c>
       <c r="B3" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135221084</v>
       </c>
       <c r="B4" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135221078</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135221072</v>
       </c>
       <c r="B6" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135221073</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135221077</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135221079</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>135221083</v>
       </c>
       <c r="B11" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135221080</v>
       </c>
       <c r="B13" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135221071</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135221074</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>135221081</v>
       </c>
       <c r="B16" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>135221085</v>
       </c>
       <c r="B17" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>135221076</v>
       </c>
       <c r="B18" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 24176-2025 artfynd.xlsx
+++ b/artfynd/A 24176-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135221075</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135221082</v>
       </c>
       <c r="B3" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135221084</v>
       </c>
       <c r="B4" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135221078</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135221072</v>
       </c>
       <c r="B6" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135221073</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135221077</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135221079</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>135221083</v>
       </c>
       <c r="B11" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>135221080</v>
       </c>
       <c r="B13" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>135221081</v>
       </c>
       <c r="B16" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>135221085</v>
       </c>
       <c r="B17" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>135221076</v>
       </c>
       <c r="B18" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 24176-2025 artfynd.xlsx
+++ b/artfynd/A 24176-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95865356</v>
+        <v>135221075</v>
       </c>
       <c r="B2" t="n">
-        <v>91872</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552745</v>
+        <v>552740</v>
       </c>
       <c r="R2" t="n">
-        <v>6946269</v>
+        <v>6946329</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95865356</t>
+          <t>https://artportalen.se/Sighting/135221075</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95865355</v>
+        <v>135221082</v>
       </c>
       <c r="B3" t="n">
-        <v>83307</v>
+        <v>83420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552656</v>
+        <v>552676</v>
       </c>
       <c r="R3" t="n">
-        <v>6946299</v>
+        <v>6946256</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,22 +887,1712 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221082</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135221084</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83420</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>308</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552610</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6946410</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221084</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135221078</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552715</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6946331</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221078</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135221072</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552711</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6946235</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221072</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>95865356</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552745</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6946269</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Veronica Jägbrant</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95865356</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135221073</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552723</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6946274</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221073</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135221077</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552718</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6946331</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221077</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135221079</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552709</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6946318</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221079</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135221083</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83411</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552609</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6946411</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221083</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95865355</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552656</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6946299</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/95865355</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135221080</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552694</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6946288</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221080</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135221071</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>552717</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6946225</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221071</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135221074</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>552743</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6946299</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221074</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135221081</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>552689</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6946286</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221081</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135221085</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>552577</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6946345</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221085</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135221076</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kalvmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>552721</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6946333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221076</t>
         </is>
       </c>
     </row>
@@ -894,6 +2600,21 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24176-2025 artfynd.xlsx
+++ b/artfynd/A 24176-2025 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135221078</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>135221081</v>
       </c>
       <c r="B16" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>135221085</v>
       </c>
       <c r="B17" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>135221076</v>
       </c>
       <c r="B18" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
